--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020090</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127020091</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020090</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127020091</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -977,6 +977,960 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127414893</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>722271</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7215359</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127415060</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105478</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>722142</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7215315</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127415061</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>722146</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7215354</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127415062</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>722252</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7215348</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering, Sumpigt parti med flera nycklar, tistel kärrfibbla mm . Starr</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127414890</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>722253</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7215229</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127414892</v>
+      </c>
+      <c r="B10" t="n">
+        <v>105478</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>722145</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7215319</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127415059</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105463</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>722192</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7215271</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127415058</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105478</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>722217</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7215294</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127414891</v>
+      </c>
+      <c r="B13" t="n">
+        <v>105463</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>722199</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7215267</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020090</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127020025</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127020091</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127414893</v>
       </c>
       <c r="B5" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>127415060</v>
       </c>
       <c r="B6" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127415061</v>
       </c>
       <c r="B7" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127415062</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127414890</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127414892</v>
       </c>
       <c r="B10" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>127415059</v>
       </c>
       <c r="B11" t="n">
-        <v>105463</v>
+        <v>105469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>127415058</v>
       </c>
       <c r="B12" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>127414891</v>
       </c>
       <c r="B13" t="n">
-        <v>105463</v>
+        <v>105469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -982,7 +982,7 @@
         <v>127414893</v>
       </c>
       <c r="B5" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>127415060</v>
       </c>
       <c r="B6" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127415061</v>
       </c>
       <c r="B7" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127415062</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127414892</v>
       </c>
       <c r="B10" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>127415059</v>
       </c>
       <c r="B11" t="n">
-        <v>105469</v>
+        <v>105471</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>127415058</v>
       </c>
       <c r="B12" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>127414891</v>
       </c>
       <c r="B13" t="n">
-        <v>105469</v>
+        <v>105471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020090</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127020025</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127020091</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127414893</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>127415060</v>
       </c>
       <c r="B6" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127415061</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127415062</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127414890</v>
       </c>
       <c r="B9" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127414892</v>
       </c>
       <c r="B10" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>127415059</v>
       </c>
       <c r="B11" t="n">
-        <v>105471</v>
+        <v>105473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>127415058</v>
       </c>
       <c r="B12" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>127414891</v>
       </c>
       <c r="B13" t="n">
-        <v>105471</v>
+        <v>105473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -982,7 +982,7 @@
         <v>127414893</v>
       </c>
       <c r="B5" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>127415060</v>
       </c>
       <c r="B6" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127415061</v>
       </c>
       <c r="B7" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127415062</v>
       </c>
       <c r="B8" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127414892</v>
       </c>
       <c r="B10" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>127415059</v>
       </c>
       <c r="B11" t="n">
-        <v>105473</v>
+        <v>105479</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>127415058</v>
       </c>
       <c r="B12" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>127414891</v>
       </c>
       <c r="B13" t="n">
-        <v>105473</v>
+        <v>105479</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -982,7 +982,7 @@
         <v>127414893</v>
       </c>
       <c r="B5" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>127415060</v>
       </c>
       <c r="B6" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127415061</v>
       </c>
       <c r="B7" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127415062</v>
       </c>
       <c r="B8" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127414890</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127414892</v>
       </c>
       <c r="B10" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>127415059</v>
       </c>
       <c r="B11" t="n">
-        <v>105479</v>
+        <v>105482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>127415058</v>
       </c>
       <c r="B12" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>127414891</v>
       </c>
       <c r="B13" t="n">
-        <v>105479</v>
+        <v>105482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -982,7 +982,7 @@
         <v>127414893</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>127415060</v>
       </c>
       <c r="B6" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127415061</v>
       </c>
       <c r="B7" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127415062</v>
       </c>
       <c r="B8" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127414890</v>
       </c>
       <c r="B9" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127414892</v>
       </c>
       <c r="B10" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>127415059</v>
       </c>
       <c r="B11" t="n">
-        <v>105482</v>
+        <v>105490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>127415058</v>
       </c>
       <c r="B12" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>127414891</v>
       </c>
       <c r="B13" t="n">
-        <v>105482</v>
+        <v>105490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -982,7 +982,7 @@
         <v>127414893</v>
       </c>
       <c r="B5" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>127415060</v>
       </c>
       <c r="B6" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>127415061</v>
       </c>
       <c r="B7" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127415062</v>
       </c>
       <c r="B8" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>127414892</v>
       </c>
       <c r="B10" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>127415059</v>
       </c>
       <c r="B11" t="n">
-        <v>105490</v>
+        <v>105491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>127415058</v>
       </c>
       <c r="B12" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>127414891</v>
       </c>
       <c r="B13" t="n">
-        <v>105490</v>
+        <v>105491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020090</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127020025</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,14 +882,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127020091</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +983,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020090</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127020025</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127020091</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1943,6 +1943,642 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129001027</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>722385</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7215236</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129001046</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>722551</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7215328</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129001026</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80229</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>722385</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7215234</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129001029</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>722338</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7215240</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129001045</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>722418</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7215298</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129001025</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80258</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>722448</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7215199</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020090</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127020025</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127020091</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>129001026</v>
       </c>
       <c r="B16" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>129001045</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>129001025</v>
       </c>
       <c r="B19" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020090</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127020091</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>129001026</v>
       </c>
       <c r="B16" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>129001045</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>129001025</v>
       </c>
       <c r="B19" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020090</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127020025</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127020091</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>129001026</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>129001045</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>129001025</v>
       </c>
       <c r="B19" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020090</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127020025</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127020091</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>129001026</v>
       </c>
       <c r="B16" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>129001045</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>129001025</v>
       </c>
       <c r="B19" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020090</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127020091</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>129001026</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>129001045</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>129001025</v>
       </c>
       <c r="B19" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127020090</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127020091</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>129001026</v>
       </c>
       <c r="B16" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>129001045</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>129001025</v>
       </c>
       <c r="B19" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -1948,7 +1948,7 @@
         <v>129001027</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129001046</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129001029</v>
       </c>
       <c r="B17" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35262-2025 artfynd.xlsx
+++ b/artfynd/A 35262-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>127020090</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -776,53 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127020025</v>
+        <v>127020091</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>722499</v>
+        <v>722493</v>
       </c>
       <c r="R3" t="n">
-        <v>7215226</v>
+        <v>7215223</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,11 +847,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,14 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127020091</v>
+        <v>129001045</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -918,17 +905,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Bjurträsk, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>722493</v>
+        <v>722418</v>
       </c>
       <c r="R4" t="n">
-        <v>7215223</v>
+        <v>7215298</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,12 +946,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,53 +971,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127414893</v>
+        <v>127414890</v>
       </c>
       <c r="B5" t="n">
-        <v>98387</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1030,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>722271</v>
+        <v>722253</v>
       </c>
       <c r="R5" t="n">
-        <v>7215359</v>
+        <v>7215229</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,32 +1089,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127415060</v>
+        <v>129001026</v>
       </c>
       <c r="B6" t="n">
-        <v>105508</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1136,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>722142</v>
+        <v>722385</v>
       </c>
       <c r="R6" t="n">
-        <v>7215315</v>
+        <v>7215234</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,12 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1203,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127415061</v>
+        <v>129001025</v>
       </c>
       <c r="B7" t="n">
-        <v>98387</v>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1242,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>722146</v>
+        <v>722448</v>
       </c>
       <c r="R7" t="n">
-        <v>7215354</v>
+        <v>7215199</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,12 +1264,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1309,49 +1301,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127415062</v>
+        <v>127020025</v>
       </c>
       <c r="B8" t="n">
-        <v>98387</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjurträsk, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>722252</v>
+        <v>722499</v>
       </c>
       <c r="R8" t="n">
-        <v>7215348</v>
+        <v>7215226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,17 +1374,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering, Sumpigt parti med flera nycklar, tistel kärrfibbla mm . Starr</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,49 +1399,53 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127414890</v>
+        <v>127414893</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>722253</v>
+        <v>722271</v>
       </c>
       <c r="R9" t="n">
-        <v>7215229</v>
+        <v>7215359</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127414892</v>
+        <v>127415061</v>
       </c>
       <c r="B10" t="n">
-        <v>105508</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>722145</v>
+        <v>722146</v>
       </c>
       <c r="R10" t="n">
-        <v>7215319</v>
+        <v>7215354</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127415059</v>
+        <v>127415062</v>
       </c>
       <c r="B11" t="n">
-        <v>105493</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1638,21 +1638,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>722192</v>
+        <v>722252</v>
       </c>
       <c r="R11" t="n">
-        <v>7215271</v>
+        <v>7215348</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering, Sumpigt parti med flera nycklar, tistel kärrfibbla mm . Starr</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,32 +1733,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127415058</v>
+        <v>129001027</v>
       </c>
       <c r="B12" t="n">
-        <v>105508</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>722217</v>
+        <v>722385</v>
       </c>
       <c r="R12" t="n">
-        <v>7215294</v>
+        <v>7215236</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1839,37 +1839,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127414891</v>
+        <v>129001029</v>
       </c>
       <c r="B13" t="n">
-        <v>105493</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>722199</v>
+        <v>722338</v>
       </c>
       <c r="R13" t="n">
-        <v>7215267</v>
+        <v>7215240</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129001027</v>
+        <v>129001046</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>722385</v>
+        <v>722551</v>
       </c>
       <c r="R14" t="n">
-        <v>7215236</v>
+        <v>7215328</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,32 +2051,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129001046</v>
+        <v>127414892</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>106244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>722551</v>
+        <v>722145</v>
       </c>
       <c r="R15" t="n">
-        <v>7215328</v>
+        <v>7215319</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2120,12 +2120,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2157,32 +2157,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129001026</v>
+        <v>127415058</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>106244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>722385</v>
+        <v>722217</v>
       </c>
       <c r="R16" t="n">
-        <v>7215234</v>
+        <v>7215294</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2263,32 +2263,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129001029</v>
+        <v>127415060</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>106244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>722338</v>
+        <v>722142</v>
       </c>
       <c r="R17" t="n">
-        <v>7215240</v>
+        <v>7215315</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2369,37 +2369,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129001045</v>
+        <v>127414891</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>106229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>722418</v>
+        <v>722199</v>
       </c>
       <c r="R18" t="n">
-        <v>7215298</v>
+        <v>7215267</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129001025</v>
+        <v>127415059</v>
       </c>
       <c r="B19" t="n">
-        <v>80178</v>
+        <v>106229</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2486,21 +2486,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>722448</v>
+        <v>722192</v>
       </c>
       <c r="R19" t="n">
-        <v>7215199</v>
+        <v>7215271</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
